--- a/ig/nr-update-image/ValueSet-as-vs-intern-id-systems.xlsx
+++ b/ig/nr-update-image/ValueSet-as-vs-intern-id-systems.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:23:26+00:00</t>
+    <t>2024-02-05T14:47:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-image/ValueSet-as-vs-intern-id-systems.xlsx
+++ b/ig/nr-update-image/ValueSet-as-vs-intern-id-systems.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:47:52+00:00</t>
+    <t>2024-02-05T14:49:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
